--- a/Decks/Necrobloom.xlsx
+++ b/Decks/Necrobloom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79059D0A-F8F3-427B-AAFF-E203382E9333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD37DC8-B93E-4DB1-8C99-9325CCA51827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Necrobloom" sheetId="1" r:id="rId1"/>
@@ -203,9 +203,6 @@
     <t>Hedge Shredder</t>
   </si>
   <si>
-    <t>Broodheart Engine</t>
-  </si>
-  <si>
     <t>Blessed Respite</t>
   </si>
   <si>
@@ -417,6 +414,9 @@
   </si>
   <si>
     <t>Deathcap Glade</t>
+  </si>
+  <si>
+    <t>Grave Researcher // Reanimate</t>
   </si>
 </sst>
 </file>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -862,10 +862,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -958,10 +958,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -974,10 +974,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -990,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -1006,10 +1006,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F21" s="4"/>
     </row>
@@ -1182,10 +1182,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1198,10 +1198,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1214,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F27" s="4"/>
     </row>
@@ -1262,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>19</v>
@@ -1422,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1438,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1758,10 +1758,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F59" s="4"/>
     </row>
@@ -1774,10 +1774,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F60" s="4"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F61" s="4"/>
     </row>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F62" s="4"/>
     </row>
@@ -1822,48 +1822,48 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="5" t="b">
         <f>C64&lt;&gt;D64</f>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1873,151 +1873,151 @@
         <v>49</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" s="5" t="b">
         <f>C73&lt;&gt;D73</f>
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F75" s="4"/>
     </row>
@@ -2103,209 +2103,209 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>69</v>
+      </c>
+      <c r="B82" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B82" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="D82" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" s="5" t="b">
         <f>C88&lt;&gt;D88</f>
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
         <v>1</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" s="5" t="b">
         <f>C93&lt;&gt;D93</f>
         <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F93" s="4"/>
     </row>
@@ -2334,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F95" s="4"/>
     </row>
@@ -2366,10 +2366,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F97" s="4"/>
     </row>
@@ -2382,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="F98" s="4"/>
     </row>
@@ -2414,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F100" s="4"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F101" s="4"/>
     </row>

--- a/Decks/Necrobloom.xlsx
+++ b/Decks/Necrobloom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD37DC8-B93E-4DB1-8C99-9325CCA51827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67A8867-9ED2-4CD7-B4FC-428B4A5FA397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="126">
   <si>
     <t>Função</t>
   </si>
@@ -323,9 +323,6 @@
     <t>Godless Shrine</t>
   </si>
   <si>
-    <t>Temple Gardens</t>
-  </si>
-  <si>
     <t>Shifting Woodland</t>
   </si>
   <si>
@@ -374,9 +371,6 @@
     <t>Ayula's Influence</t>
   </si>
   <si>
-    <t>Emeria Shepherd</t>
-  </si>
-  <si>
     <t>Woodland Acolyte // Mend the Wilds</t>
   </si>
   <si>
@@ -410,13 +404,16 @@
     <t>Tainted Wood</t>
   </si>
   <si>
-    <t>Shattered Sacntum</t>
-  </si>
-  <si>
     <t>Deathcap Glade</t>
   </si>
   <si>
     <t>Grave Researcher // Reanimate</t>
+  </si>
+  <si>
+    <t>Temple Garden</t>
+  </si>
+  <si>
+    <t>Shattered Sanctum</t>
   </si>
 </sst>
 </file>
@@ -958,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -974,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -990,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -1006,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -1134,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1150,10 +1147,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" s="4"/>
     </row>
@@ -1182,10 +1179,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1198,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1214,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1246,10 +1243,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F27" s="4"/>
     </row>
@@ -1262,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>19</v>
@@ -1774,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>68</v>
@@ -1790,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F61" s="4"/>
     </row>
@@ -1806,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>67</v>
@@ -1886,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>86</v>
@@ -1966,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>77</v>
@@ -1982,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>73</v>
@@ -2107,10 +2104,10 @@
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>87</v>
@@ -2142,7 +2139,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>83</v>
@@ -2158,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>75</v>
@@ -2174,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>72</v>
@@ -2222,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>85</v>
@@ -2270,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>88</v>
@@ -2286,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>76</v>
@@ -2302,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>84</v>
@@ -2382,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F98" s="4"/>
     </row>

--- a/Decks/Necrobloom.xlsx
+++ b/Decks/Necrobloom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67A8867-9ED2-4CD7-B4FC-428B4A5FA397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560FF872-4EF7-418C-80FE-F230F5C04528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="124">
   <si>
     <t>Função</t>
   </si>
@@ -344,9 +344,6 @@
     <t>Canopy Vista</t>
   </si>
   <si>
-    <t>Grismold, the Dreadsower</t>
-  </si>
-  <si>
     <t>Mythos of Nethroi</t>
   </si>
   <si>
@@ -378,9 +375,6 @@
   </si>
   <si>
     <t>Rumor Gatherer</t>
-  </si>
-  <si>
-    <t>Uurg, Spawn of Turg</t>
   </si>
   <si>
     <t>Woodland Cemetery</t>
@@ -955,10 +949,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -971,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -987,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -1003,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>101</v>
@@ -1131,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>96</v>
@@ -1147,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>97</v>
@@ -1179,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>95</v>
@@ -1243,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>98</v>
@@ -1259,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>19</v>
@@ -1771,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>68</v>
@@ -1787,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F61" s="4"/>
     </row>
@@ -1803,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>67</v>
@@ -1883,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>86</v>
@@ -1960,10 +1954,10 @@
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>77</v>
@@ -1979,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>73</v>
@@ -2139,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>83</v>
@@ -2155,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>75</v>
@@ -2171,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>72</v>
@@ -2219,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>85</v>
@@ -2264,10 +2258,10 @@
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>88</v>
@@ -2283,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>76</v>
@@ -2299,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>84</v>
@@ -2379,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F98" s="4"/>
     </row>

--- a/Decks/Necrobloom.xlsx
+++ b/Decks/Necrobloom.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560FF872-4EF7-418C-80FE-F230F5C04528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F7CF4E-1245-4A8F-AC44-37151BB91B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
   <si>
     <t>Função</t>
   </si>
@@ -185,9 +185,6 @@
     <t>Ulamog, the Infinite Gyre</t>
   </si>
   <si>
-    <t>Gaea's Blessing</t>
-  </si>
-  <si>
     <t>Lotus Petal</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>Six</t>
   </si>
   <si>
-    <t>Hedge Shredder</t>
-  </si>
-  <si>
     <t>Blessed Respite</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
     <t>Sylvan Library</t>
   </si>
   <si>
-    <t>Ramunap Excavator</t>
-  </si>
-  <si>
     <t>Worldly Tutor</t>
   </si>
   <si>
@@ -266,9 +257,6 @@
     <t>Loot, Exuberant Explorer</t>
   </si>
   <si>
-    <t>The Gitrog, Ravenous Ride</t>
-  </si>
-  <si>
     <t>Fecund Greenshell</t>
   </si>
   <si>
@@ -341,63 +329,24 @@
     <t>Thespian's Stage</t>
   </si>
   <si>
-    <t>Canopy Vista</t>
-  </si>
-  <si>
     <t>Mythos of Nethroi</t>
   </si>
   <si>
     <t>Harsh Annotation</t>
   </si>
   <si>
-    <t>Splendid Reclamation</t>
-  </si>
-  <si>
-    <t>World Shaper</t>
-  </si>
-  <si>
-    <t>Crawling Infestation</t>
-  </si>
-  <si>
-    <t>Cemetery Tampering</t>
-  </si>
-  <si>
-    <t>Nyx Weaver</t>
-  </si>
-  <si>
-    <t>Ayula's Influence</t>
-  </si>
-  <si>
     <t>Woodland Acolyte // Mend the Wilds</t>
   </si>
   <si>
     <t>Tocasia's Welcome</t>
   </si>
   <si>
-    <t>Rumor Gatherer</t>
-  </si>
-  <si>
     <t>Woodland Cemetery</t>
   </si>
   <si>
-    <t>Fabled Passage</t>
-  </si>
-  <si>
-    <t>Demolition Field</t>
-  </si>
-  <si>
     <t>Llanowar Wastes</t>
   </si>
   <si>
-    <t>Hickory Woodlot</t>
-  </si>
-  <si>
-    <t>Ghost Quarter</t>
-  </si>
-  <si>
-    <t>Tainted Wood</t>
-  </si>
-  <si>
     <t>Deathcap Glade</t>
   </si>
   <si>
@@ -408,6 +357,33 @@
   </si>
   <si>
     <t>Shattered Sanctum</t>
+  </si>
+  <si>
+    <t>Horizon Explorer</t>
+  </si>
+  <si>
+    <t>Ecological Appreciation</t>
+  </si>
+  <si>
+    <t>Flagstones of Trokair</t>
+  </si>
+  <si>
+    <t>Mole Man, Moloid Master</t>
+  </si>
+  <si>
+    <t>Ruin Ghost</t>
+  </si>
+  <si>
+    <t>Cauldron of Essence</t>
+  </si>
+  <si>
+    <t>Quarteirão Fantasma</t>
+  </si>
+  <si>
+    <t>Campo de Demolição</t>
+  </si>
+  <si>
+    <t>Bountiful Promenade</t>
   </si>
 </sst>
 </file>
@@ -837,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -853,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -933,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -949,10 +925,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -965,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -981,10 +957,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -994,13 +970,13 @@
       </c>
       <c r="B12" s="5" t="b">
         <f>C12&lt;&gt;D12</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -1122,13 +1098,13 @@
       </c>
       <c r="B20" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1141,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F21" s="4"/>
     </row>
@@ -1173,10 +1149,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1189,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1205,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1234,13 +1210,13 @@
       </c>
       <c r="B27" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F27" s="4"/>
     </row>
@@ -1253,7 +1229,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>19</v>
@@ -1269,10 +1245,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1413,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1429,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1445,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1749,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F59" s="4"/>
     </row>
@@ -1765,10 +1741,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F60" s="4"/>
     </row>
@@ -1781,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F61" s="4"/>
     </row>
@@ -1797,10 +1773,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F62" s="4"/>
     </row>
@@ -1813,202 +1789,202 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B64" s="5" t="b">
         <f>C64&lt;&gt;D64</f>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B73" s="5" t="b">
         <f>C73&lt;&gt;D73</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F75" s="4"/>
     </row>
@@ -2021,10 +1997,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F76" s="4"/>
     </row>
@@ -2037,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F77" s="4"/>
     </row>
@@ -2094,247 +2070,247 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>66</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B88" s="5" t="b">
         <f>C88&lt;&gt;D88</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B93" s="5" t="b">
         <f>C93&lt;&gt;D93</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="F94" s="4"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
@@ -2350,81 +2326,81 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B97" s="5" t="b">
         <f>C97&lt;&gt;D97</f>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F97" s="4"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>51</v>
+      </c>
+      <c r="B99" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B99" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="D99" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F99" s="4"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F101" s="4"/>
     </row>

--- a/Decks/Necrobloom.xlsx
+++ b/Decks/Necrobloom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F7CF4E-1245-4A8F-AC44-37151BB91B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAFAF86-91E2-4B44-A731-6429320809B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Necrobloom" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>Bountiful Promenade</t>
+  </si>
+  <si>
+    <t>The Queen of Dale</t>
   </si>
 </sst>
 </file>
@@ -1962,13 +1965,13 @@
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>71</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="F74" s="4"/>
     </row>
